--- a/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_01_21_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_01_21_Cau.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>60</v>
@@ -804,7 +804,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xem hệ thống chỉ tạo một đầu ra hay còn quan sát và hành động qua nhiều bước để đạt mục tiêu.</t>
+          <t>Hệ thống nhận mục tiêu, tự kiểm tra lịch của 4 người, đề xuất giờ, gửi lời mời qua công cụ và xác nhận trạng thái là hệ thống có hành vi tác nhân (agentic) vì nó tự lập kế hoạch và hành động qua nhiều bước để đạt mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -859,7 +859,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng gọi một hệ thống là agent chỉ vì nó có thể sinh nội dung. Tìm các trường hợp tạo nội dung mới rồi kết thúc sau một lượt xử lý.</t>
+          <t>Mô hình viết đoạn mô tả từ yêu cầu rồi kết thúc (a) và mô hình tạo ảnh từ mô tả rồi kết thúc (c) là các hệ thống sinh nội dung (generative) nhưng chỉ chạy một lượt và không có vòng lặp kế hoạch, công cụ hay trạng thái của một agent.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -907,7 +907,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh việc viết quy tắc thủ công với việc để mô hình học biểu diễn từ dữ liệu.</t>
+          <t>Mô hình tạo sinh quy mô lớn thành công nhờ khả năng học biểu diễn từ lượng dữ liệu khổng lồ bằng năng lực tính toán và kiến trúc Transformer, chứ không phải do mở rộng các bộ quy tắc thủ công của con người.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">
@@ -1020,7 +1020,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách chức năng do ứng dụng tổ chức quanh mô hình khỏi cơ chế bên trong chính mô hình đó.</t>
+          <t>Khi thay thế foundation model, lớp ứng dụng/sản phẩm cần tự vận hành gồm: Xác thực và hạn ngạch người dùng (a), Giao diện trò chuyện (b), và Quy tắc kiểm duyệt nội dung của ứng dụng (c). Cơ chế attention và trọng số thuộc về chính mô hình nền tảng.</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1068,7 +1068,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm đặc điểm cho phép hệ thống tiếp tục hành động sau phản hồi đầu tiên.</t>
+          <t>Hệ thống A chỉ gọi LLM một lượt để viết email nên là ứng dụng gọi LLM đơn thuần; Hệ thống B có mục tiêu, kế hoạch, công cụ (CRM, lịch) và trạng thái nên là một agent đầy đủ.</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o3 → o1 → o4 → o5</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không cập nhật trạng thái đặt vé trước khi công cụ xác nhận đổi vé thành công.</t>
+          <t>Vòng xử lý hợp lý bắt đầu từ lập kế hoạch gọi công cụ đổi vé (o2) -&gt; thực thi gọi công cụ ticket.change (o3) -&gt; nhận kết quả đổi vé thành công X9 (o1) -&gt; cập nhật trạng thái đặt vé thành X9 (o4) -&gt; thông báo kết quả rồi dừng (o5).</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1324,7 +1324,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt việc cập nhật chuỗi đầu vào với việc cập nhật trọng số của mô hình.</t>
+          <t>Trong mô hình tự hồi quy (autoregressive language model), sau khi chọn token 'mưa', token này được nối trực tiếp vào chuỗi ngữ cảnh đầu vào (context) để làm đầu vào cho lượt dự đoán token kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1375,7 +1375,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dung lượng ngữ cảnh được tính theo token của cách biểu diễn dữ liệu, không theo ý nghĩa trừu tượng.</t>
+          <t>JSON tốn 820 token trong khi Bảng rút gọn tốn 510 token cho cùng thông tin, do đó Bảng rút gọn tiết kiệm 820 - 510 = 310 token ngữ cảnh cho mỗi lần gửi.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1428,7 +1428,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ xét những đặc trưng thực sự nằm trong chuỗi đầu vào của tokenizer.</t>
+          <t>Các yếu tố trong chuỗi đầu vào làm thay đổi số token gồm: Ngôn ngữ và vốn từ tokenizer đã học (a), Dấu câu và khoảng trắng (b), Ký hiệu cú pháp cấu trúc như JSON/code (c), và Thuật toán tách mảnh từ (e). Màu nền của editor (d) không được gửi vào tokenizer nên không ảnh hưởng.</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1480,7 +1480,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh đơn vị mà `split()` đếm với đơn vị mà mô hình xử lý.</t>
+          <t>Dùng `tokenizer.encode()` chính xác hơn `len(text.split())` vì tokenizer sử dụng đúng từ điển và thuật toán tách mảnh từ (BPE/WordPiece) của mô hình, đếm chính xác số đơn vị token mà mô hình thực sự nhận.</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1572,7 +1572,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh nhóm nào có kết quả đa dạng hơn dựa trên đầu ra quan sát được.</t>
+          <t>Khi chỉ temperature thay đổi, nhóm Y đa dạng hơn và có câu lạc đề chứng tỏ nhóm Y được chạy với temperature cao hơn nhóm X (temperature cao làm phẳng phân phối xác suất và tăng tính ngẫu nhiên).</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -1685,7 +1685,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dừng ở token làm tổng xác suất tích lũy lần đầu đạt hoặc vượt ngưỡng.</t>
+          <t>Các token sắp xếp giảm dần: K = 0,50; L = 0,20; M = 0,15... Với top-p = 0,68, tổng tích lũy: K = 0,50 (&lt; 0,68); K + L = 0,70 (&gt;= 0,68). Vậy tập nhỏ nhất được giữ lại gồm {K, L}.</t>
         </is>
       </c>
     </row>
